--- a/stories/arbres/TREE-SEC-006.xlsx
+++ b/stories/arbres/TREE-SEC-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Nino est à la maison avec Maman. Ils vont sur le balcon. Nino reste derrière la protection. Ses pieds restent au sol. Ses mains tiennent un jouet. Maman est l'adulte, tout près. Papa est dans la cuisine.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. L'air est frais. Nino est sur le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la cuisine. Un oiseau chante. Ils regardent vers la cuisine, tout près. Nino a les pieds au sol, derrière la protection, avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2599,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2713,6 +2770,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Une casserole tinte. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2937,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3108,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. La cloche d'un vélo. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3275,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3446,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Un chat miaule. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3613,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3784,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi le jardin. Le vent est doux. Ils regardent le jardin, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3883,6 +3975,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4049,6 +4146,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. La cloche d'un vélo. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4211,6 +4313,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4377,6 +4484,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Un chat miaule. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4539,6 +4651,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4705,6 +4822,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. L'eau coule loin. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4867,6 +4989,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5033,6 +5160,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la chambre. Une casserole tinte. Ils restent près de la chambre, sur le balcon. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5219,6 +5351,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5385,6 +5522,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Un chat miaule. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5547,6 +5689,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5713,6 +5860,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. L'eau coule loin. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5875,6 +6027,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6041,6 +6198,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Un oiseau chante. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6203,6 +6365,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6369,6 +6536,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Nino est sur le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6553,6 +6725,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
     </row>
@@ -6725,6 +6902,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6911,6 +7093,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7077,6 +7264,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la cuisine. La cloche d'un vélo. Ils regardent vers la cuisine, tout près. Nino a les pieds au sol, derrière la protection, avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,6 +7455,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7429,6 +7626,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. La cloche d'un vélo. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7591,6 +7793,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7757,6 +7964,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Un chat miaule. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7919,6 +8131,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8085,6 +8302,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. L'eau coule loin. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8247,6 +8469,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8413,6 +8640,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi le jardin. Un chat miaule. Ils regardent le jardin, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8599,6 +8831,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8765,6 +9002,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Un chat miaule. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8927,6 +9169,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9093,6 +9340,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. L'eau coule loin. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9255,6 +9507,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9421,6 +9678,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Un oiseau chante. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9583,6 +9845,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9749,6 +10016,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la chambre. L'eau coule loin. Ils restent près de la chambre, sur le balcon. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9935,6 +10207,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10101,6 +10378,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. L'eau coule loin. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10263,6 +10545,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10429,6 +10716,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Un oiseau chante. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10591,6 +10883,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10757,6 +11054,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Le vent est doux. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10919,6 +11221,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11085,6 +11392,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. La lumière est douce. Nino est sur le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11269,6 +11581,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
     </row>
@@ -11441,6 +11758,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11627,6 +11949,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11793,6 +12120,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la cuisine. Un oiseau chante. Ils regardent vers la cuisine, tout près. Nino a les pieds au sol, derrière la protection, avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11979,6 +12311,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12145,6 +12482,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Un chat miaule. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12307,6 +12649,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12473,6 +12820,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. L'eau coule loin. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12635,6 +12987,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12801,6 +13158,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Un oiseau chante. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12963,6 +13325,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13129,6 +13496,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi le jardin. Le vent est doux. Ils regardent le jardin, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13315,6 +13687,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13481,6 +13858,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. L'eau coule loin. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13643,6 +14025,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13809,6 +14196,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Un oiseau chante. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13971,6 +14363,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14137,6 +14534,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Le vent est doux. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14299,6 +14701,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14465,6 +14872,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a choisi la chambre. Une casserole tinte. Ils restent près de la chambre, sur le balcon. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14651,6 +15063,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14817,6 +15234,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le ballon rouge. Un oiseau chante. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14979,6 +15401,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15145,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le seau bleu. Le vent est doux. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15307,6 +15739,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15473,6 +15910,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nino prend le doudou. Une casserole tinte. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15635,6 +16077,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15653,7 +16100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15670,6 +16117,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-006.xlsx
+++ b/stories/arbres/TREE-SEC-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Nino est à la maison avec Maman. Ils vont sur le balcon. Nino reste derrière la protection. Ses pieds restent au sol. Ses mains tiennent un jouet. Maman est l'adulte, tout près. Papa est dans la cuisine.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|C'est le matin. L'air est frais. Nino est sur le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2060,7 @@
           <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2424,7 @@
           <t>narrateur|Nino a choisi la cuisine. Un oiseau chante. Ils regardent vers la cuisine, tout près. Nino a les pieds au sol, derrière la protection, avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2604,6 +2616,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2775,6 +2788,7 @@
           <t>narrateur|Nino prend le ballon rouge. Une casserole tinte. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2942,6 +2956,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3113,6 +3128,7 @@
           <t>narrateur|Nino prend le seau bleu. La cloche d'un vélo. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3280,6 +3296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3451,6 +3468,7 @@
           <t>narrateur|Nino prend le doudou. Un chat miaule. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3618,6 +3636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3789,6 +3808,7 @@
           <t>narrateur|Nino a choisi le jardin. Le vent est doux. Ils regardent le jardin, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3980,6 +4000,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4151,6 +4172,7 @@
           <t>narrateur|Nino prend le ballon rouge. La cloche d'un vélo. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4318,6 +4340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4489,6 +4512,7 @@
           <t>narrateur|Nino prend le seau bleu. Un chat miaule. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4656,6 +4680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4827,6 +4852,7 @@
           <t>narrateur|Nino prend le doudou. L'eau coule loin. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4994,6 +5020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5165,6 +5192,7 @@
           <t>narrateur|Nino a choisi la chambre. Une casserole tinte. Ils restent près de la chambre, sur le balcon. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5356,6 +5384,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5527,6 +5556,7 @@
           <t>narrateur|Nino prend le ballon rouge. Un chat miaule. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5694,6 +5724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5865,6 +5896,7 @@
           <t>narrateur|Nino prend le seau bleu. L'eau coule loin. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6032,6 +6064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6203,6 +6236,7 @@
           <t>narrateur|Nino prend le doudou. Un oiseau chante. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6370,6 +6404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6541,6 +6576,7 @@
           <t>narrateur|C'est après la sieste. Nino est sur le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6732,6 +6768,7 @@
           <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6907,6 +6944,7 @@
           <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7098,6 +7136,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7269,6 +7308,7 @@
           <t>narrateur|Nino a choisi la cuisine. La cloche d'un vélo. Ils regardent vers la cuisine, tout près. Nino a les pieds au sol, derrière la protection, avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7460,6 +7500,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7631,6 +7672,7 @@
           <t>narrateur|Nino prend le ballon rouge. La cloche d'un vélo. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7798,6 +7840,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7969,6 +8012,7 @@
           <t>narrateur|Nino prend le seau bleu. Un chat miaule. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8136,6 +8180,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8307,6 +8352,7 @@
           <t>narrateur|Nino prend le doudou. L'eau coule loin. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8474,6 +8520,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8645,6 +8692,7 @@
           <t>narrateur|Nino a choisi le jardin. Un chat miaule. Ils regardent le jardin, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8836,6 +8884,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9007,6 +9056,7 @@
           <t>narrateur|Nino prend le ballon rouge. Un chat miaule. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9174,6 +9224,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9345,6 +9396,7 @@
           <t>narrateur|Nino prend le seau bleu. L'eau coule loin. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9512,6 +9564,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9683,6 +9736,7 @@
           <t>narrateur|Nino prend le doudou. Un oiseau chante. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9850,6 +9904,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10021,6 +10076,7 @@
           <t>narrateur|Nino a choisi la chambre. L'eau coule loin. Ils restent près de la chambre, sur le balcon. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10212,6 +10268,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10383,6 +10440,7 @@
           <t>narrateur|Nino prend le ballon rouge. L'eau coule loin. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10550,6 +10608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10721,6 +10780,7 @@
           <t>narrateur|Nino prend le seau bleu. Un oiseau chante. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10888,6 +10948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11059,6 +11120,7 @@
           <t>narrateur|Nino prend le doudou. Le vent est doux. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11226,6 +11288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11397,6 +11460,7 @@
           <t>narrateur|C'est le soir. La lumière est douce. Nino est sur le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11588,6 +11652,7 @@
           <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11763,6 +11828,7 @@
           <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11954,6 +12020,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12125,6 +12192,7 @@
           <t>narrateur|Nino a choisi la cuisine. Un oiseau chante. Ils regardent vers la cuisine, tout près. Nino a les pieds au sol, derrière la protection, avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12316,6 +12384,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12487,6 +12556,7 @@
           <t>narrateur|Nino prend le ballon rouge. Un chat miaule. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12654,6 +12724,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12825,6 +12896,7 @@
           <t>narrateur|Nino prend le seau bleu. L'eau coule loin. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12992,6 +13064,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13163,6 +13236,7 @@
           <t>narrateur|Nino prend le doudou. Un oiseau chante. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13330,6 +13404,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13501,6 +13576,7 @@
           <t>narrateur|Nino a choisi le jardin. Le vent est doux. Ils regardent le jardin, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13692,6 +13768,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13863,6 +13940,7 @@
           <t>narrateur|Nino prend le ballon rouge. L'eau coule loin. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14030,6 +14108,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14201,6 +14280,7 @@
           <t>narrateur|Nino prend le seau bleu. Un oiseau chante. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14368,6 +14448,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14539,6 +14620,7 @@
           <t>narrateur|Nino prend le doudou. Le vent est doux. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14706,6 +14788,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14877,6 +14960,7 @@
           <t>narrateur|Nino a choisi la chambre. Une casserole tinte. Ils restent près de la chambre, sur le balcon. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15068,6 +15152,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15239,6 +15324,7 @@
           <t>narrateur|Nino prend le ballon rouge. Un oiseau chante. Nino tient le ballon rouge. Pieds au sol, derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15406,6 +15492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15577,6 +15664,7 @@
           <t>narrateur|Nino prend le seau bleu. Le vent est doux. Nino tient le seau bleu. Pieds au sol, avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15744,6 +15832,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15915,6 +16004,7 @@
           <t>narrateur|Nino prend le doudou. Une casserole tinte. Nino tient le doudou. Pieds au sol, derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Nino dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16082,6 +16172,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16100,7 +16191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16124,6 +16215,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16325,6 +16430,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
